--- a/01_data_model/02_DSD/input_dsd.xlsx
+++ b/01_data_model/02_DSD/input_dsd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanniejo\Documents_local\01_dataplatform\021_SVbevraging\01_code\01_data_model\02_DSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BFCD64-89CE-4D9B-98F7-B64105EA09F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6BADA4-1AC2-44D9-BF26-73A4144F81AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2127" uniqueCount="1538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2295" uniqueCount="1674">
   <si>
     <t>concept_id</t>
   </si>
@@ -4635,13 +4635,421 @@
   </si>
   <si>
     <t>^SV[0-9]{4}-PUF-[0-9]{4}$</t>
+  </si>
+  <si>
+    <t>timer_start</t>
+  </si>
+  <si>
+    <t>timer_socdem</t>
+  </si>
+  <si>
+    <t>timer_mem</t>
+  </si>
+  <si>
+    <t>timer_volunt</t>
+  </si>
+  <si>
+    <t>timer_cult</t>
+  </si>
+  <si>
+    <t>timer_spt</t>
+  </si>
+  <si>
+    <t>timer_lifesat</t>
+  </si>
+  <si>
+    <t>timer_wb</t>
+  </si>
+  <si>
+    <t>Timer Start vragenlijst</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module socio-demografische variabelen</t>
+  </si>
+  <si>
+    <t>Timer start</t>
+  </si>
+  <si>
+    <t>Timer sociodemografie</t>
+  </si>
+  <si>
+    <t>Timer verenigingen</t>
+  </si>
+  <si>
+    <t>Timer vrijwilligerswerk</t>
+  </si>
+  <si>
+    <t>Timer cultuurparticipatie</t>
+  </si>
+  <si>
+    <t>Timer sportparticipatie</t>
+  </si>
+  <si>
+    <t>Timer levenstevredenheid</t>
+  </si>
+  <si>
+    <t>Timer welzijn</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>Minuteur début</t>
+  </si>
+  <si>
+    <t>Minuteur sociodémographie</t>
+  </si>
+  <si>
+    <t>Minuteur associations</t>
+  </si>
+  <si>
+    <t>Minuteur bénévolat</t>
+  </si>
+  <si>
+    <t>Minuteur participation culturelle</t>
+  </si>
+  <si>
+    <t>Minuteur participation sportive</t>
+  </si>
+  <si>
+    <t>Minuteur satisfaction de vie</t>
+  </si>
+  <si>
+    <t>Minuteur bien-être</t>
+  </si>
+  <si>
+    <t>Timer sociodemographics</t>
+  </si>
+  <si>
+    <t>Timer associations</t>
+  </si>
+  <si>
+    <t>Timer volunteering</t>
+  </si>
+  <si>
+    <t>Timer cultural participation</t>
+  </si>
+  <si>
+    <t>Timer sport participation</t>
+  </si>
+  <si>
+    <t>Timer life satisfaction</t>
+  </si>
+  <si>
+    <t>Timer well-being</t>
+  </si>
+  <si>
+    <t>timer_saf</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module  Veiligheidsgevoelens en mijdgedrag</t>
+  </si>
+  <si>
+    <t>timer_cnt</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Sociale Contacten</t>
+  </si>
+  <si>
+    <t>timer_icare</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Informele Zorg</t>
+  </si>
+  <si>
+    <t>timer_tinst</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Vertrouwen in instellingen</t>
+  </si>
+  <si>
+    <t>timer_stf</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Tevredenheid met voorzieningen</t>
+  </si>
+  <si>
+    <t>timer_nois</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Geluidshinder</t>
+  </si>
+  <si>
+    <t>timer_igov</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Imago Overheden</t>
+  </si>
+  <si>
+    <t>timer_polsat</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Tevredenheid met het Beleid</t>
+  </si>
+  <si>
+    <t>timer_cfgov</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Tevredenheid informatie en communicatie</t>
+  </si>
+  <si>
+    <t>timer_tgov</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Vertrouwen in de overheid</t>
+  </si>
+  <si>
+    <t>timer_strust</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Vertrouwen in de medemens</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Actief lidmaatschap van verenigingen</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Vrijwilligerswerk</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Cultuurparticipatie</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Sportparticipatie</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Levenstevredenheid</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module welzijnAlgemeen welbevinden</t>
+  </si>
+  <si>
+    <t>timer_hap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timer na afmaken module </t>
+  </si>
+  <si>
+    <t>timer_fex</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Toekomstverwachtingen</t>
+  </si>
+  <si>
+    <t>timer_res</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Veerkracht</t>
+  </si>
+  <si>
+    <t>timer_dev</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Mediabezit</t>
+  </si>
+  <si>
+    <t>timer_sub</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Internetbezit</t>
+  </si>
+  <si>
+    <t>timer_net</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Mediagebruik</t>
+  </si>
+  <si>
+    <t>timer_med</t>
+  </si>
+  <si>
+    <t>timer_nws</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Nieuwsgebruik</t>
+  </si>
+  <si>
+    <t>timer_pa</t>
+  </si>
+  <si>
+    <t>Timer na afmaken module Politieke participatie</t>
+  </si>
+  <si>
+    <t>Timer veiligheid/mijdgedrag</t>
+  </si>
+  <si>
+    <t>Timer sociale contacten</t>
+  </si>
+  <si>
+    <t>Timer informele zorg</t>
+  </si>
+  <si>
+    <t>Timer imago overheden</t>
+  </si>
+  <si>
+    <t>Timer tevredenheid beleid</t>
+  </si>
+  <si>
+    <t>Timer info &amp; communicatie</t>
+  </si>
+  <si>
+    <t>Timer vertrouwen overheid</t>
+  </si>
+  <si>
+    <t>Timer vertrouwen medemens</t>
+  </si>
+  <si>
+    <t>Timer geluk</t>
+  </si>
+  <si>
+    <t>Timer toekomstverwachtingen</t>
+  </si>
+  <si>
+    <t>Timer veerkracht</t>
+  </si>
+  <si>
+    <t>Timer mediabezit</t>
+  </si>
+  <si>
+    <t>Timer internetbezit</t>
+  </si>
+  <si>
+    <t>Timer mediagebruik</t>
+  </si>
+  <si>
+    <t>Timer nieuwsgebruik</t>
+  </si>
+  <si>
+    <t>Timer politieke participatie</t>
+  </si>
+  <si>
+    <t>Timer vertrouwen instellingen</t>
+  </si>
+  <si>
+    <t>Timer tevredenheid voorzieningen</t>
+  </si>
+  <si>
+    <t>Timer geluidshinder</t>
+  </si>
+  <si>
+    <t>Minuteur sécurité/évitement</t>
+  </si>
+  <si>
+    <t>Minuteur contacts sociaux</t>
+  </si>
+  <si>
+    <t>Minuteur soins informels</t>
+  </si>
+  <si>
+    <t>Minuteur image des autorités</t>
+  </si>
+  <si>
+    <t>Minuteur satisfaction politique</t>
+  </si>
+  <si>
+    <t>Minuteur info &amp; communication</t>
+  </si>
+  <si>
+    <t>Minuteur confiance gouvernement</t>
+  </si>
+  <si>
+    <t>Minuteur confiance envers autrui</t>
+  </si>
+  <si>
+    <t>Minuteur bonheur</t>
+  </si>
+  <si>
+    <t>Minuteur perspectives d'avenir</t>
+  </si>
+  <si>
+    <t>Minuteur résilience</t>
+  </si>
+  <si>
+    <t>Minuteur possession de médias</t>
+  </si>
+  <si>
+    <t>Minuteur possession internet</t>
+  </si>
+  <si>
+    <t>Minuteur usage des médias</t>
+  </si>
+  <si>
+    <t>Minuteur usage des actualités</t>
+  </si>
+  <si>
+    <t>Minuteur participation politique</t>
+  </si>
+  <si>
+    <t>Minuteur confiance institutions</t>
+  </si>
+  <si>
+    <t>Minuteur satisfaction équipements</t>
+  </si>
+  <si>
+    <t>Minuteur nuisances sonores</t>
+  </si>
+  <si>
+    <t>Timer safety/avoidance</t>
+  </si>
+  <si>
+    <t>Timer social contacts</t>
+  </si>
+  <si>
+    <t>Timer informal care</t>
+  </si>
+  <si>
+    <t>Timer government image</t>
+  </si>
+  <si>
+    <t>Timer policy satisfaction</t>
+  </si>
+  <si>
+    <t>Timer info &amp; communication</t>
+  </si>
+  <si>
+    <t>Timer trust in government</t>
+  </si>
+  <si>
+    <t>Timer trust in others</t>
+  </si>
+  <si>
+    <t>Timer happiness</t>
+  </si>
+  <si>
+    <t>Timer future expectations</t>
+  </si>
+  <si>
+    <t>Timer resilience</t>
+  </si>
+  <si>
+    <t>Timer media ownership</t>
+  </si>
+  <si>
+    <t>Timer internet ownership</t>
+  </si>
+  <si>
+    <t>Timer media use</t>
+  </si>
+  <si>
+    <t>Timer news use</t>
+  </si>
+  <si>
+    <t>Timer political participation</t>
+  </si>
+  <si>
+    <t>Timer trust in institutions</t>
+  </si>
+  <si>
+    <t>Timer satisfaction with facilities</t>
+  </si>
+  <si>
+    <t>Timer noise nuisance</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4653,6 +5061,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4678,7 +5092,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4686,6 +5100,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4990,7 +5408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K307"/>
+  <dimension ref="A1:K335"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -12985,7 +13403,652 @@
         <v>0</v>
       </c>
     </row>
+    <row r="308" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A308" s="3" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B308" s="3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C308" s="3" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D308" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="E308" s="3" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K308" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A309" s="3" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B309" s="3" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C309" s="3" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D309" s="3" t="s">
+        <v>1558</v>
+      </c>
+      <c r="E309" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F309" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K309" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A310" s="3" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B310" s="3" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C310" s="3" t="s">
+        <v>1617</v>
+      </c>
+      <c r="D310" s="3" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E310" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K310" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A311" s="3" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B311" s="3" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C311" s="3" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D311" s="3" t="s">
+        <v>1637</v>
+      </c>
+      <c r="E311" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K311" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A312" s="3" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B312" s="3" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C312" s="3" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D312" s="3" t="s">
+        <v>1638</v>
+      </c>
+      <c r="E312" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K312" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A313" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B313" s="3" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C313" s="3" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D313" s="3" t="s">
+        <v>1639</v>
+      </c>
+      <c r="E313" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F313" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K313" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A314" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B314" s="3" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C314" s="3" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D314" s="3" t="s">
+        <v>1640</v>
+      </c>
+      <c r="E314" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F314" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K314" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A315" s="3" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B315" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C315" s="3" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D315" s="3" t="s">
+        <v>1641</v>
+      </c>
+      <c r="E315" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F315" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K315" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A316" s="3" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B316" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C316" s="3" t="s">
+        <v>1623</v>
+      </c>
+      <c r="D316" s="3" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E316" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F316" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K316" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A317" s="3" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B317" s="3" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C317" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D317" s="3" t="s">
+        <v>1643</v>
+      </c>
+      <c r="E317" s="3" t="s">
+        <v>1662</v>
+      </c>
+      <c r="F317" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K317" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A318" s="3" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B318" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C318" s="3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D318" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="E318" s="3" t="s">
+        <v>1566</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K318" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A319" s="3" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B319" s="3" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C319" s="3" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D319" s="3" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E319" s="3" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F319" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K319" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A320" s="3" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B320" s="3" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C320" s="3" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D320" s="3" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E320" s="3" t="s">
+        <v>1568</v>
+      </c>
+      <c r="F320" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K320" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A321" s="3" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B321" s="3" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C321" s="3" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D321" s="3" t="s">
+        <v>1562</v>
+      </c>
+      <c r="E321" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F321" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K321" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A322" s="3" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B322" s="3" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C322" s="3" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D322" s="3" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E322" s="3" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F322" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K322" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A323" s="3" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B323" s="3" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C323" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D323" s="3" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E323" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F323" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K323" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A324" s="3" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B324" s="3" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C324" s="3" t="s">
+        <v>1625</v>
+      </c>
+      <c r="D324" s="3" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E324" s="3" t="s">
+        <v>1663</v>
+      </c>
+      <c r="F324" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K324" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A325" s="3" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B325" s="3" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C325" s="3" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D325" s="3" t="s">
+        <v>1645</v>
+      </c>
+      <c r="E325" s="3" t="s">
+        <v>1664</v>
+      </c>
+      <c r="F325" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K325" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A326" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B326" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C326" s="3" t="s">
+        <v>1627</v>
+      </c>
+      <c r="D326" s="3" t="s">
+        <v>1646</v>
+      </c>
+      <c r="E326" s="3" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F326" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K326" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A327" s="3" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B327" s="3" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C327" s="3" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D327" s="3" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E327" s="3" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F327" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K327" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A328" s="3" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B328" s="3" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C328" s="3" t="s">
+        <v>1629</v>
+      </c>
+      <c r="D328" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="E328" s="3" t="s">
+        <v>1667</v>
+      </c>
+      <c r="F328" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K328" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A329" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B329" s="3" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C329" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D329" s="3" t="s">
+        <v>1649</v>
+      </c>
+      <c r="E329" s="3" t="s">
+        <v>1668</v>
+      </c>
+      <c r="F329" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K329" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A330" s="3" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B330" s="3" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C330" s="3" t="s">
+        <v>1629</v>
+      </c>
+      <c r="D330" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="E330" s="3" t="s">
+        <v>1667</v>
+      </c>
+      <c r="F330" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K330" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A331" s="3" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B331" s="3" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C331" s="3" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D331" s="3" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E331" s="3" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F331" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K331" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A332" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C332" s="3" t="s">
+        <v>1632</v>
+      </c>
+      <c r="D332" s="3" t="s">
+        <v>1651</v>
+      </c>
+      <c r="E332" s="3" t="s">
+        <v>1670</v>
+      </c>
+      <c r="F332" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K332" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A333" s="3" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B333" s="3" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C333" s="3" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D333" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E333" s="3" t="s">
+        <v>1671</v>
+      </c>
+      <c r="F333" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K333" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A334" s="3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B334" s="3" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C334" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D334" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E334" s="3" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F334" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K334" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A335" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B335" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C335" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D335" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E335" s="3" t="s">
+        <v>1673</v>
+      </c>
+      <c r="F335" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K335" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>